--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -9,11 +9,14 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$26</definedName>
+  </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="236">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T10:02:53+00:00</t>
+    <t>2026-02-23T08:57:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -358,7 +361,7 @@
 </t>
   </si>
   <si>
-    <t>The order of the dosage instructions</t>
+    <t>Die Reihenfolge der Dosierungsanweisungen. Entfällt bei Einzeldosierung.</t>
   </si>
   <si>
     <t>Indicates the order in which the dosage instructions should be applied or interpreted.</t>
@@ -376,7 +379,7 @@
     <t>Dosage.text</t>
   </si>
   <si>
-    <t>Free text dosage instructions e.g. SIG</t>
+    <t>Freitext-Dosierungsanweisung, wenn keine strukturierte Angabe möglich ist.</t>
   </si>
   <si>
     <t>Free text dosage instructions e.g. SIG.</t>
@@ -395,7 +398,8 @@
 </t>
   </si>
   <si>
-    <t>Supplemental instruction or warnings to the patient - e.g. "with meals", "may cause drowsiness"</t>
+    <t>Codierte Anweisungen oder Warnhinweise für den Patienten, z.B. zur Einnahme oder zur Aufbewahrung des Arzneimittels. (ex):
+https://hl7.org/fhir/R4/valueset-additional-instruction-codes.html. TODO: Nur wenn nicht ohnehin im Beipackzettel enthalten oder zusätzlich? Evtl. f. magistrale Zubereitungen, da kein Beipackzettel.</t>
   </si>
   <si>
     <t>Supplemental instructions to the patient on how to take the medication  (e.g. "with meals" or"take half to one hour before food") or warnings for the patient about the medication (e.g. "may cause drowsiness" or "avoid exposure of skin to direct sunlight or sunlamps").</t>
@@ -422,7 +426,7 @@
     <t>Dosage.patientInstruction</t>
   </si>
   <si>
-    <t>Patient or consumer oriented instructions</t>
+    <t>Freitext Anweisungen für den Patienten, z.B. zur Einnahme oder zur Aufbewahrung des Arzneimittels.</t>
   </si>
   <si>
     <t>Instructions in terms that are understood by the patient or consumer.</t>
@@ -435,7 +439,8 @@
 </t>
   </si>
   <si>
-    <t>When medication should be administered</t>
+    <t>Zeitpunkt oder Zeitraum der Einnahme des Medikaments. 
+Um widersprüchliche Anweisungen zu vermeiden, ist entweder Dosage.timing oder Dosage.text zu befüllen.</t>
   </si>
   <si>
     <t>When medication should be administered.</t>
@@ -453,8 +458,8 @@
     <t>Dosage.asNeeded[x]</t>
   </si>
   <si>
-    <t>boolean
-CodeableConcept</t>
+    <t xml:space="preserve">boolean
+</t>
   </si>
   <si>
     <t>Take "as needed" (for x)</t>
@@ -472,16 +477,41 @@
     <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
+    <t xml:space="preserve">type:$this}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
     <t>.outboundRelationship[typeCode=PRCN].target[classCode=OBS, moodCode=EVN, code="as needed"].value=boolean or codable concept</t>
   </si>
   <si>
     <t>TQ1-9</t>
   </si>
   <si>
+    <t>Dosage.asNeeded[x]:asNeededBoolean</t>
+  </si>
+  <si>
+    <t>asNeededBoolean</t>
+  </si>
+  <si>
+    <t>Bedarfsmedikation: Ja/Nein</t>
+  </si>
+  <si>
+    <t>Dosage.asNeeded[x]:asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>asNeededCodeableConcept</t>
+  </si>
+  <si>
+    <t>Bedarfsmedikation: Grund für die Bedarfsmedikation; Vermutlich reicht ein genereller Grund für die Medikation im Planeintrag (wenn e-Diagnose verfügbar).</t>
+  </si>
+  <si>
     <t>Dosage.site</t>
   </si>
   <si>
-    <t>Body site to administer to</t>
+    <t>Körperstelle, an der das Medikament angewendet wird, z.B. Haut, Auge, Ohr etc.</t>
   </si>
   <si>
     <t>Body site to administer to.</t>
@@ -508,7 +538,7 @@
     <t>Dosage.route</t>
   </si>
   <si>
-    <t>How drug should enter body</t>
+    <t>Verabreichungsweg, z.B. oral, nasal, intravenös, subkutan etc.</t>
   </si>
   <si>
     <t>How drug should enter body.</t>
@@ -517,10 +547,10 @@
     <t>A code specifying the route or physiological path of administration of a therapeutic agent into or onto a patient's body.</t>
   </si>
   <si>
-    <t>A coded concept describing the route or physiological path of administration of a therapeutic agent into or onto the body of a subject.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/route-codes|4.0.1</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/CodeSystem/medikationartanwendung</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -532,7 +562,7 @@
     <t>Dosage.method</t>
   </si>
   <si>
-    <t>Technique for administering medication</t>
+    <t xml:space="preserve">Verabreichungsmethode, z.B. Infusion, Injektion, Tablette, Salbe etc. </t>
   </si>
   <si>
     <t>Technique for administering medication.</t>
@@ -563,7 +593,7 @@
 </t>
   </si>
   <si>
-    <t>Amount of medication administered</t>
+    <t>Menge des verabreichten Medikaments</t>
   </si>
   <si>
     <t>The amount of medication administered.</t>
@@ -619,6 +649,19 @@
   </si>
   <si>
     <t>RXO-2, RXE-3</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity</t>
+  </si>
+  <si>
+    <t>doseQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity}
+</t>
+  </si>
+  <si>
+    <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.rate[x]</t>
@@ -833,6 +876,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1014,12 +1072,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL23"/>
+  <dimension ref="A1:AL26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="28.78515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.59765625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="28.78515625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.63671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1042,7 +1100,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="169.7734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="51.89453125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -1172,7 +1230,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>31</v>
       </c>
@@ -1278,7 +1336,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>83</v>
       </c>
@@ -1384,7 +1442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>90</v>
       </c>
@@ -1492,7 +1550,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -1621,7 +1679,7 @@
         <v>84</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
@@ -1729,7 +1787,7 @@
         <v>84</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I7" t="s" s="2">
         <v>21</v>
@@ -1818,7 +1876,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>121</v>
       </c>
@@ -1928,7 +1986,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>131</v>
       </c>
@@ -2053,7 +2111,7 @@
         <v>84</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
@@ -2144,7 +2202,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>141</v>
       </c>
@@ -2219,16 +2277,14 @@
         <v>21</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>141</v>
@@ -2246,20 +2302,22 @@
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>153</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
@@ -2271,7 +2329,7 @@
         <v>84</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
@@ -2280,20 +2338,18 @@
         <v>103</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="O12" t="s" s="2">
-        <v>154</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -2317,13 +2373,13 @@
         <v>21</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>155</v>
+        <v>21</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>156</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>21</v>
@@ -2341,7 +2397,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -2356,20 +2412,22 @@
         <v>81</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="D13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2378,7 +2436,7 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -2393,15 +2451,15 @@
         <v>122</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" t="s" s="2">
-        <v>162</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2428,10 +2486,10 @@
         <v>127</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
@@ -2449,7 +2507,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2464,18 +2522,18 @@
         <v>81</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2501,16 +2559,16 @@
         <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2538,10 +2596,10 @@
         <v>127</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -2559,7 +2617,7 @@
         <v>21</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -2574,18 +2632,18 @@
         <v>81</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2596,7 +2654,7 @@
         <v>76</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>21</v>
@@ -2608,16 +2666,18 @@
         <v>103</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="O15" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
       </c>
@@ -2641,13 +2701,11 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -2665,13 +2723,13 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>21</v>
@@ -2680,18 +2738,18 @@
         <v>81</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2711,19 +2769,23 @@
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
       </c>
@@ -2747,13 +2809,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>21</v>
+        <v>181</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -2771,7 +2833,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>88</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -2783,25 +2845,25 @@
         <v>21</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>89</v>
+        <v>182</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>21</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2811,26 +2873,24 @@
         <v>77</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>92</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>93</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>95</v>
-      </c>
+        <v>187</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -2867,19 +2927,19 @@
         <v>21</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>96</v>
+        <v>21</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>99</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -2891,21 +2951,21 @@
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2925,21 +2985,19 @@
         <v>21</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>87</v>
       </c>
       <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>186</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
       </c>
@@ -2963,13 +3021,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>127</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>187</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -2987,7 +3045,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>183</v>
+        <v>88</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -2999,16 +3057,16 @@
         <v>21</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>190</v>
       </c>
@@ -3017,14 +3075,14 @@
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
@@ -3033,23 +3091,21 @@
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>191</v>
+        <v>92</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>193</v>
+        <v>94</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>195</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3085,45 +3141,45 @@
         <v>21</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3146,19 +3202,17 @@
         <v>103</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3183,13 +3237,13 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>21</v>
+        <v>127</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>21</v>
+        <v>196</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>21</v>
@@ -3207,7 +3261,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3222,18 +3276,18 @@
         <v>81</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3256,19 +3310,19 @@
         <v>103</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3305,19 +3359,17 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC21" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3332,20 +3384,22 @@
         <v>81</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
@@ -3357,7 +3411,7 @@
         <v>84</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
@@ -3366,19 +3420,19 @@
         <v>103</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3403,13 +3457,11 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>21</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -3427,7 +3479,7 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3442,18 +3494,18 @@
         <v>81</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3476,17 +3528,19 @@
         <v>103</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3535,7 +3589,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3550,13 +3604,359 @@
         <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="24" hidden="true">
+      <c r="A24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="M24" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK24" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" hidden="true">
+      <c r="A25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="P25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" hidden="true">
+      <c r="A26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="P26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK26" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="AL26" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AL26">
+    <filterColumn colId="7">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="27">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI25">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$37</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="299">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:57:08+00:00</t>
+    <t>2026-02-23T17:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -435,7 +435,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing
+    <t xml:space="preserve">Timing {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-timing}
 </t>
   </si>
   <si>
@@ -538,7 +538,8 @@
     <t>Dosage.route</t>
   </si>
   <si>
-    <t>Verabreichungsweg, z.B. oral, nasal, intravenös, subkutan etc.</t>
+    <t>Art der Anwendung der Arznei. (z.B. oral, nasal, intravenös, subkutan)
+ Kann bei codierten Arzneien aus der ASP-Liste entnommen werden.</t>
   </si>
   <si>
     <t>How drug should enter body.</t>
@@ -611,7 +612,7 @@
     <t>Dosage.doseAndRate.type</t>
   </si>
   <si>
-    <t>The kind of dose or rate specified</t>
+    <t>Art der Dosierung, z.B. berechnet, wie verordnet (ex): https://hl7.org/fhir/R4/valueset-dose-rate-type.html</t>
   </si>
   <si>
     <t>The kind of dose or rate specified, for example, ordered or calculated.</t>
@@ -636,7 +637,7 @@
 Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
-    <t>Amount of medication per dose</t>
+    <t>Menge des verabreichten Medikaments pro Zeiteinheit.</t>
   </si>
   <si>
     <t>Amount of medication per dose.</t>
@@ -649,6 +650,19 @@
   </si>
   <si>
     <t>RXO-2, RXE-3</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseRange</t>
+  </si>
+  <si>
+    <t>doseRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Dosierungsspanne wird mit low und high angegeben, z.B. 5-10 mg.</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.dose[x]:doseQuantity</t>
@@ -661,7 +675,167 @@
 </t>
   </si>
   <si>
+    <t>Mapping auf doseQuantity</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity.id</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x].id</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity.extension</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x].extension</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity.value</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x].value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decimal
+</t>
+  </si>
+  <si>
+    <t>Numerical value (with implicit precision)</t>
+  </si>
+  <si>
+    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
+  </si>
+  <si>
+    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
+  </si>
+  <si>
+    <t>Precision is handled implicitly in almost all cases of measurement.</t>
+  </si>
+  <si>
+    <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
+  </si>
+  <si>
+    <t>SN.2  / CQ - N/A</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity.comparator</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x].comparator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>&lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+  </si>
+  <si>
+    <t>Not allowed to be used in this context</t>
+  </si>
+  <si>
+    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
+  </si>
+  <si>
+    <t>If there is no comparator, then there is no modification of the value</t>
+  </si>
+  <si>
+    <t>How the Quantity should be understood and represented.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
+  </si>
+  <si>
+    <t>Quantity.comparator</t>
+  </si>
+  <si>
+    <t>IVL properties</t>
+  </si>
+  <si>
+    <t>SN.1  / CQ.1</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity.unit</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x].unit</t>
+  </si>
+  <si>
+    <t>Unit representation</t>
+  </si>
+  <si>
+    <t>A human-readable form of the unit.</t>
+  </si>
+  <si>
+    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
+  </si>
+  <si>
     <t>https://termgit.elga.gv.at/ValueSet-elga-medikationmengenart</t>
+  </si>
+  <si>
+    <t>Quantity.unit</t>
+  </si>
+  <si>
+    <t>PQ.unit</t>
+  </si>
+  <si>
+    <t>(see OBX.6 etc.) / CQ.2</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity.system</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x].system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>System that defines coded unit form</t>
+  </si>
+  <si>
+    <t>The identification of the system that provides the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>Quantity.system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty-3
+</t>
+  </si>
+  <si>
+    <t>CO.codeSystem, PQ.translation.codeSystem</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x]:doseQuantity.code</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.dose[x].code</t>
+  </si>
+  <si>
+    <t>Coded form of the unit</t>
+  </si>
+  <si>
+    <t>A computer processable form of the unit in some unit representation system.</t>
+  </si>
+  <si>
+    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
+  </si>
+  <si>
+    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
+  </si>
+  <si>
+    <t>Quantity.code</t>
+  </si>
+  <si>
+    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Dosage.doseAndRate.rate[x]</t>
@@ -691,11 +865,32 @@
     <t>RXE22, RXE23, RXE-24</t>
   </si>
   <si>
-    <t>Dosage.maxDosePerPeriod</t>
+    <t>Dosage.doseAndRate.rate[x]:rateRatio</t>
+  </si>
+  <si>
+    <t>rateRatio</t>
   </si>
   <si>
     <t xml:space="preserve">Ratio
 </t>
+  </si>
+  <si>
+    <t>TODO: prüfen</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.rate[x]:rateRange</t>
+  </si>
+  <si>
+    <t>rateRange</t>
+  </si>
+  <si>
+    <t>Dosage.doseAndRate.rate[x]:rateQuantity</t>
+  </si>
+  <si>
+    <t>rateQuantity</t>
+  </si>
+  <si>
+    <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
     <t>Upper limit on medication per unit of time</t>
@@ -1072,11 +1267,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL26"/>
+  <dimension ref="A1:AL37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="28.78515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.88671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="33.8203125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.63671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1085,7 +1280,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="31.890625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.30078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2638,7 +2833,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>167</v>
       </c>
@@ -2657,7 +2852,7 @@
         <v>84</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
@@ -2744,7 +2939,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>175</v>
       </c>
@@ -2763,7 +2958,7 @@
         <v>84</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -2870,7 +3065,7 @@
         <v>76</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>103</v>
@@ -3366,7 +3561,7 @@
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>198</v>
@@ -3423,7 +3618,7 @@
         <v>207</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="M22" t="s" s="2">
         <v>201</v>
@@ -3457,11 +3652,13 @@
         <v>21</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y22" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>208</v>
+        <v>21</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>21</v>
@@ -3500,14 +3697,16 @@
         <v>204</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>209</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
@@ -3519,7 +3718,7 @@
         <v>84</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -3528,19 +3727,19 @@
         <v>103</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3589,7 +3788,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -3604,18 +3803,18 @@
         <v>81</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>215</v>
+        <v>182</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3635,23 +3834,19 @@
         <v>21</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>21</v>
       </c>
@@ -3699,7 +3894,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>88</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -3711,32 +3906,32 @@
         <v>21</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>223</v>
+        <v>89</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>224</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -3745,23 +3940,21 @@
         <v>21</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>92</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>93</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
+        <v>94</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>230</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
       </c>
@@ -3797,34 +3990,34 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>89</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
@@ -3832,10 +4025,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3858,17 +4051,19 @@
         <v>103</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O26" t="s" s="2">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -3917,7 +4112,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -3932,14 +4127,1220 @@
         <v>81</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>231</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="N27" s="2"/>
+      <c r="O27" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="P28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="Y28" s="2"/>
+      <c r="Z28" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" hidden="true">
+      <c r="A30" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="P30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK30" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31" hidden="true">
+      <c r="A31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="P31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AC31" s="2"/>
+      <c r="AD31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="D32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="P32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C33" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="D33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="P33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="34" hidden="true">
+      <c r="A34" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="D34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="P34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="P35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="P37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL26">
+  <autoFilter ref="A1:AL37">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -3949,7 +5350,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI25">
+  <conditionalFormatting sqref="A2:AI36">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="298">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Dosage</t>
+    <t>Dosage</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>Type</t>
-  </si>
-  <si>
-    <t>Dosage</t>
   </si>
   <si>
     <t>Base Definition</t>
@@ -1233,31 +1230,31 @@
         <v>30</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>36</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1311,126 +1308,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s" s="1">
         <v>38</v>
       </c>
-      <c r="B1" t="s" s="1">
+      <c r="C1" t="s" s="1">
         <v>39</v>
       </c>
-      <c r="C1" t="s" s="1">
+      <c r="D1" t="s" s="1">
         <v>40</v>
       </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>41</v>
       </c>
-      <c r="E1" t="s" s="1">
+      <c r="F1" t="s" s="1">
         <v>42</v>
       </c>
-      <c r="F1" t="s" s="1">
+      <c r="G1" t="s" s="1">
         <v>43</v>
       </c>
-      <c r="G1" t="s" s="1">
+      <c r="H1" t="s" s="1">
         <v>44</v>
       </c>
-      <c r="H1" t="s" s="1">
+      <c r="I1" t="s" s="1">
         <v>45</v>
       </c>
-      <c r="I1" t="s" s="1">
+      <c r="J1" t="s" s="1">
         <v>46</v>
       </c>
-      <c r="J1" t="s" s="1">
+      <c r="K1" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="K1" t="s" s="1">
+      <c r="L1" t="s" s="1">
         <v>48</v>
       </c>
-      <c r="L1" t="s" s="1">
+      <c r="M1" t="s" s="1">
         <v>49</v>
       </c>
-      <c r="M1" t="s" s="1">
+      <c r="N1" t="s" s="1">
         <v>50</v>
       </c>
-      <c r="N1" t="s" s="1">
+      <c r="O1" t="s" s="1">
         <v>51</v>
       </c>
-      <c r="O1" t="s" s="1">
+      <c r="P1" t="s" s="1">
         <v>52</v>
       </c>
-      <c r="P1" t="s" s="1">
+      <c r="Q1" t="s" s="1">
         <v>53</v>
       </c>
-      <c r="Q1" t="s" s="1">
+      <c r="R1" t="s" s="1">
         <v>54</v>
       </c>
-      <c r="R1" t="s" s="1">
+      <c r="S1" t="s" s="1">
         <v>55</v>
       </c>
-      <c r="S1" t="s" s="1">
+      <c r="T1" t="s" s="1">
         <v>56</v>
       </c>
-      <c r="T1" t="s" s="1">
+      <c r="U1" t="s" s="1">
         <v>57</v>
       </c>
-      <c r="U1" t="s" s="1">
+      <c r="V1" t="s" s="1">
         <v>58</v>
       </c>
-      <c r="V1" t="s" s="1">
+      <c r="W1" t="s" s="1">
         <v>59</v>
       </c>
-      <c r="W1" t="s" s="1">
+      <c r="X1" t="s" s="1">
         <v>60</v>
       </c>
-      <c r="X1" t="s" s="1">
+      <c r="Y1" t="s" s="1">
         <v>61</v>
       </c>
-      <c r="Y1" t="s" s="1">
+      <c r="Z1" t="s" s="1">
         <v>62</v>
       </c>
-      <c r="Z1" t="s" s="1">
+      <c r="AA1" t="s" s="1">
         <v>63</v>
       </c>
-      <c r="AA1" t="s" s="1">
+      <c r="AB1" t="s" s="1">
         <v>64</v>
       </c>
-      <c r="AB1" t="s" s="1">
+      <c r="AC1" t="s" s="1">
         <v>65</v>
       </c>
-      <c r="AC1" t="s" s="1">
+      <c r="AD1" t="s" s="1">
         <v>66</v>
       </c>
-      <c r="AD1" t="s" s="1">
+      <c r="AE1" t="s" s="1">
         <v>67</v>
       </c>
-      <c r="AE1" t="s" s="1">
+      <c r="AF1" t="s" s="1">
         <v>68</v>
       </c>
-      <c r="AF1" t="s" s="1">
+      <c r="AG1" t="s" s="1">
         <v>69</v>
       </c>
-      <c r="AG1" t="s" s="1">
+      <c r="AH1" t="s" s="1">
         <v>70</v>
       </c>
-      <c r="AH1" t="s" s="1">
+      <c r="AI1" t="s" s="1">
         <v>71</v>
       </c>
-      <c r="AI1" t="s" s="1">
+      <c r="AJ1" t="s" s="1">
         <v>72</v>
       </c>
-      <c r="AJ1" t="s" s="1">
+      <c r="AK1" t="s" s="1">
         <v>73</v>
       </c>
-      <c r="AK1" t="s" s="1">
+      <c r="AL1" t="s" s="1">
         <v>74</v>
-      </c>
-      <c r="AL1" t="s" s="1">
-        <v>75</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1438,28 +1435,28 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G2" t="s" s="2">
+      <c r="H2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K2" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="H2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s" s="2">
+      <c r="L2" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="L2" t="s" s="2">
+      <c r="M2" t="s" s="2">
         <v>79</v>
-      </c>
-      <c r="M2" t="s" s="2">
-        <v>80</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1510,22 +1507,22 @@
         <v>21</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="AG2" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH2" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AH2" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AI2" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ2" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK2" t="s" s="2">
         <v>81</v>
-      </c>
-      <c r="AK2" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AL2" t="s" s="2">
         <v>21</v>
@@ -1533,10 +1530,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1544,28 +1541,28 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L3" t="s" s="2">
+      <c r="M3" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M3" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1616,22 +1613,22 @@
         <v>21</v>
       </c>
       <c r="AF3" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK3" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AG3" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH3" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ3" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK3" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>21</v>
@@ -1639,22 +1636,22 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G4" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G4" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H4" t="s" s="2">
         <v>21</v>
       </c>
@@ -1665,16 +1662,16 @@
         <v>21</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L4" t="s" s="2">
+      <c r="M4" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M4" t="s" s="2">
+      <c r="N4" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N4" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
@@ -1712,34 +1709,34 @@
         <v>21</v>
       </c>
       <c r="AB4" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC4" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC4" t="s" s="2">
+      <c r="AD4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE4" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE4" t="s" s="2">
+      <c r="AF4" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AF4" t="s" s="2">
+      <c r="AG4" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH4" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI4" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ4" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AG4" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH4" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI4" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ4" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK4" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AL4" t="s" s="2">
         <v>21</v>
@@ -1747,45 +1744,45 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G5" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G5" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H5" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="J5" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K5" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L5" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="J5" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K5" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L5" t="s" s="2">
+      <c r="M5" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="M5" t="s" s="2">
+      <c r="N5" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O5" t="s" s="2">
         <v>105</v>
-      </c>
-      <c r="N5" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O5" t="s" s="2">
-        <v>106</v>
       </c>
       <c r="P5" t="s" s="2">
         <v>21</v>
@@ -1834,22 +1831,22 @@
         <v>21</v>
       </c>
       <c r="AF5" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG5" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH5" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI5" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ5" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK5" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="AG5" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH5" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI5" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ5" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK5" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="AL5" t="s" s="2">
         <v>21</v>
@@ -1857,10 +1854,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1868,32 +1865,32 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L6" t="s" s="2">
+      <c r="M6" t="s" s="2">
         <v>111</v>
-      </c>
-      <c r="M6" t="s" s="2">
-        <v>112</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P6" t="s" s="2">
         <v>21</v>
@@ -1942,33 +1939,33 @@
         <v>21</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK6" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AL6" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="AL6" t="s" s="2">
-        <v>115</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1976,32 +1973,32 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L7" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>117</v>
-      </c>
-      <c r="M7" t="s" s="2">
-        <v>118</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>21</v>
@@ -2050,33 +2047,33 @@
         <v>21</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2084,11 +2081,11 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G8" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G8" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H8" t="s" s="2">
         <v>21</v>
       </c>
@@ -2096,22 +2093,22 @@
         <v>21</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>123</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="N8" t="s" s="2">
+      <c r="O8" t="s" s="2">
         <v>125</v>
-      </c>
-      <c r="O8" t="s" s="2">
-        <v>126</v>
       </c>
       <c r="P8" t="s" s="2">
         <v>21</v>
@@ -2136,57 +2133,57 @@
         <v>21</v>
       </c>
       <c r="X8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="Y8" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="Y8" t="s" s="2">
+      <c r="Z8" t="s" s="2">
         <v>128</v>
       </c>
-      <c r="Z8" t="s" s="2">
+      <c r="AA8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AA8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF8" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AL8" t="s" s="2">
-        <v>130</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2194,28 +2191,28 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L9" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>132</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>133</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2266,33 +2263,33 @@
         <v>21</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2300,34 +2297,34 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L10" t="s" s="2">
+      <c r="M10" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="M10" t="s" s="2">
+      <c r="N10" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="N10" t="s" s="2">
+      <c r="O10" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>21</v>
@@ -2376,22 +2373,22 @@
         <v>21</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AL10" t="s" s="2">
         <v>21</v>
@@ -2399,10 +2396,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2410,10 +2407,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
@@ -2422,19 +2419,19 @@
         <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="M11" t="s" s="2">
+      <c r="N11" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2460,89 +2457,89 @@
         <v>21</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="Z11" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="Z11" t="s" s="2">
+      <c r="AA11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB11" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE11" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK11" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="AF11" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK11" t="s" s="2">
+      <c r="AL11" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C12" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N12" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2592,46 +2589,46 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AL12" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="C13" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>21</v>
@@ -2640,19 +2637,19 @@
         <v>21</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>144</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2678,14 +2675,14 @@
         <v>21</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y13" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="Z13" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="Z13" t="s" s="2">
-        <v>147</v>
-      </c>
       <c r="AA13" t="s" s="2">
         <v>21</v>
       </c>
@@ -2702,33 +2699,33 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>151</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2736,10 +2733,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>21</v>
@@ -2748,22 +2745,22 @@
         <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>159</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="O14" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -2788,57 +2785,57 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="Z14" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="Z14" t="s" s="2">
+      <c r="AA14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG14" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH14" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI14" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ14" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK14" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="AA14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="AG14" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI14" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ14" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK14" t="s" s="2">
+      <c r="AL14" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="AL14" t="s" s="2">
-        <v>166</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2846,32 +2843,32 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -2896,55 +2893,55 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AA15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF15" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK15" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK15" t="s" s="2">
+      <c r="AL15" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>174</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2952,34 +2949,34 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>177</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3004,57 +3001,57 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Z16" t="s" s="2">
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF16" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="AG16" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ16" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="AA16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK16" t="s" s="2">
+      <c r="AL16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="AL16" t="s" s="2">
-        <v>183</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3062,28 +3059,28 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3134,33 +3131,33 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH17" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AH17" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AI17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3168,28 +3165,28 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K18" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K18" t="s" s="2">
+      <c r="L18" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3240,22 +3237,22 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>21</v>
@@ -3263,22 +3260,22 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G19" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G19" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H19" t="s" s="2">
         <v>21</v>
       </c>
@@ -3289,16 +3286,16 @@
         <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3336,34 +3333,34 @@
         <v>21</v>
       </c>
       <c r="AB19" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC19" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC19" t="s" s="2">
+      <c r="AD19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE19" t="s" s="2">
+      <c r="AF19" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AF19" t="s" s="2">
+      <c r="AG19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AG19" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI19" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ19" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK19" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
@@ -3371,10 +3368,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3382,10 +3379,10 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>21</v>
@@ -3394,20 +3391,20 @@
         <v>21</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>21</v>
@@ -3432,57 +3429,57 @@
         <v>21</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Y20" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="Z20" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="Z20" t="s" s="2">
+      <c r="AA20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>197</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3490,10 +3487,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>21</v>
@@ -3502,22 +3499,22 @@
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -3554,80 +3551,80 @@
         <v>21</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AC21" s="2"/>
       <c r="AD21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C22" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="B22" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>206</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>208</v>
-      </c>
       <c r="M22" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="O22" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>21</v>
@@ -3676,70 +3673,70 @@
         <v>21</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C23" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B23" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C23" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>212</v>
-      </c>
       <c r="M23" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N23" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>21</v>
@@ -3788,33 +3785,33 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="B24" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="B24" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3822,28 +3819,28 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="K24" t="s" s="2">
+      <c r="L24" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>86</v>
-      </c>
-      <c r="M24" t="s" s="2">
-        <v>87</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3894,22 +3891,22 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>89</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>21</v>
@@ -3917,22 +3914,22 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="B25" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="B25" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G25" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="G25" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
       </c>
@@ -3943,16 +3940,16 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>95</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3990,34 +3987,34 @@
         <v>21</v>
       </c>
       <c r="AB25" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AC25" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="AC25" t="s" s="2">
+      <c r="AD25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE25" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="AD25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE25" t="s" s="2">
+      <c r="AF25" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AF25" t="s" s="2">
+      <c r="AG25" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
         <v>99</v>
       </c>
-      <c r="AG25" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI25" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ25" t="s" s="2">
-        <v>100</v>
-      </c>
       <c r="AK25" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
@@ -4025,10 +4022,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="B26" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="B26" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4036,10 +4033,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>21</v>
@@ -4048,22 +4045,22 @@
         <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>222</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>223</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>21</v>
@@ -4112,33 +4109,33 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AG26" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>226</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4146,109 +4143,109 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>230</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>231</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="P27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q27" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="P27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q27" t="s" s="2">
+      <c r="R27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="R27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X27" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="Z27" t="s" s="2">
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
+      <c r="AG27" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK27" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AG27" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH27" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ27" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK27" t="s" s="2">
+      <c r="AL27" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>238</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4256,32 +4253,32 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="H28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J28" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="K28" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="L28" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>21</v>
@@ -4306,55 +4303,55 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AA28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF28" t="s" s="2">
+      <c r="AG28" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK28" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK28" t="s" s="2">
+      <c r="AL28" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>247</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4362,10 +4359,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>21</v>
@@ -4374,20 +4371,20 @@
         <v>21</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>21</v>
@@ -4436,33 +4433,33 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI29" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI29" t="s" s="2">
+      <c r="AJ29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK29" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AJ29" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>256</v>
-      </c>
       <c r="AL29" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4470,10 +4467,10 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>21</v>
@@ -4482,22 +4479,22 @@
         <v>21</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4546,33 +4543,33 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK30" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AG30" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI30" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ30" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AK30" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="AL30" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4580,10 +4577,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>21</v>
@@ -4592,22 +4589,22 @@
         <v>21</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L31" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -4644,56 +4641,56 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL31" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C32" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>21</v>
@@ -4702,22 +4699,22 @@
         <v>21</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="M32" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -4766,46 +4763,46 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL32" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C33" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>278</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>21</v>
@@ -4814,22 +4811,22 @@
         <v>21</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M33" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -4878,46 +4875,46 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="C34" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>21</v>
@@ -4926,22 +4923,22 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M34" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="N34" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -4990,33 +4987,33 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>272</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5024,10 +5021,10 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
@@ -5036,22 +5033,22 @@
         <v>21</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5100,33 +5097,33 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5134,10 +5131,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>21</v>
@@ -5146,22 +5143,22 @@
         <v>21</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N36" t="s" s="2">
+      <c r="O36" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5210,22 +5207,22 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>21</v>
@@ -5233,10 +5230,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5244,10 +5241,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>21</v>
@@ -5256,20 +5253,20 @@
         <v>21</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5318,22 +5315,22 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T12:22:28+00:00</t>
+    <t>2026-03-06T14:18:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:31:06+00:00</t>
+    <t>2026-03-16T16:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T16:50:24+00:00</t>
+    <t>2026-03-19T16:44:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -535,8 +535,7 @@
     <t>Dosage.route</t>
   </si>
   <si>
-    <t>Art der Anwendung der Arznei. (z.B. oral, nasal, intravenös, subkutan)
- Kann bei codierten Arzneien aus der ASP-Liste entnommen werden.</t>
+    <t>Art der Anwendung der Arznei. (z.B. oral, nasal, intravenös, subkutan). Kann bei codierten Arzneien aus der ASP-Liste entnommen werden.</t>
   </si>
   <si>
     <t>How drug should enter body.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T16:44:44+00:00</t>
+    <t>2026-03-20T13:50:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T10:00:40+00:00</t>
+    <t>2026-03-24T15:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T14:44:53+00:00</t>
+    <t>2026-04-13T15:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T10:13:14+00:00</t>
+    <t>2026-04-17T19:15:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$34</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1314" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="291">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T08:20:06+00:00</t>
+    <t>2026-04-20T16:24:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -396,7 +396,7 @@
   </si>
   <si>
     <t>Codierte Anweisungen oder Warnhinweise für den Patienten, z.B. zur Einnahme oder zur Aufbewahrung des Arzneimittels. (ex):
-https://hl7.org/fhir/R4/valueset-additional-instruction-codes.html. TODO: Nur wenn nicht ohnehin im Beipackzettel enthalten oder zusätzlich? Evtl. f. magistrale Zubereitungen, da kein Beipackzettel.</t>
+https://hl7.org/fhir/R4/valueset-additional-instruction-codes.html.</t>
   </si>
   <si>
     <t>Supplemental instructions to the patient on how to take the medication  (e.g. "with meals" or"take half to one hour before food") or warnings for the patient about the medication (e.g. "may cause drowsiness" or "avoid exposure of skin to direct sunlight or sunlamps").</t>
@@ -502,7 +502,7 @@
     <t>asNeededCodeableConcept</t>
   </si>
   <si>
-    <t>Bedarfsmedikation: Grund für die Bedarfsmedikation; Vermutlich reicht ein genereller Grund für die Medikation im Planeintrag (wenn e-Diagnose verfügbar).</t>
+    <t>Bedarfsmedikation: Grund für die Bedarfsmedikation</t>
   </si>
   <si>
     <t>Dosage.site</t>
@@ -559,7 +559,7 @@
     <t>Dosage.method</t>
   </si>
   <si>
-    <t xml:space="preserve">Verabreichungsmethode, z.B. Infusion, Injektion, Tablette, Salbe etc. </t>
+    <t>Verabreichungsmethode, z.B. Infusion, Injektion, Tablette, Salbe etc.</t>
   </si>
   <si>
     <t>Technique for administering medication.</t>
@@ -861,32 +861,11 @@
     <t>RXE22, RXE23, RXE-24</t>
   </si>
   <si>
-    <t>Dosage.doseAndRate.rate[x]:rateRatio</t>
-  </si>
-  <si>
-    <t>rateRatio</t>
+    <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
     <t xml:space="preserve">Ratio
 </t>
-  </si>
-  <si>
-    <t>TODO: prüfen</t>
-  </si>
-  <si>
-    <t>Dosage.doseAndRate.rate[x]:rateRange</t>
-  </si>
-  <si>
-    <t>rateRange</t>
-  </si>
-  <si>
-    <t>Dosage.doseAndRate.rate[x]:rateQuantity</t>
-  </si>
-  <si>
-    <t>rateQuantity</t>
-  </si>
-  <si>
-    <t>Dosage.maxDosePerPeriod</t>
   </si>
   <si>
     <t>Upper limit on medication per unit of time</t>
@@ -1263,7 +1242,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL37"/>
+  <dimension ref="A1:AL34"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.88671875" customWidth="true" bestFit="true"/>
@@ -4640,14 +4619,16 @@
         <v>21</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>264</v>
@@ -4676,11 +4657,9 @@
         <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>21</v>
       </c>
@@ -4701,19 +4680,19 @@
         <v>102</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>267</v>
-      </c>
       <c r="N32" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -4762,7 +4741,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4777,22 +4756,20 @@
         <v>80</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>21</v>
       </c>
@@ -4813,19 +4790,19 @@
         <v>102</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>206</v>
+        <v>281</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>21</v>
@@ -4874,7 +4851,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -4889,22 +4866,20 @@
         <v>80</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>271</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>279</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>21</v>
       </c>
@@ -4925,19 +4900,17 @@
         <v>102</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>210</v>
+        <v>281</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>21</v>
@@ -4986,7 +4959,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5001,342 +4974,14 @@
         <v>80</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="C35" s="2"/>
-      <c r="D35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="P35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" hidden="true">
-      <c r="A36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C36" s="2"/>
-      <c r="D36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J36" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="K36" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="P36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF36" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AG36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH36" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI36" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ36" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK36" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" hidden="true">
-      <c r="A37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="I37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J37" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="K37" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="P37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AG37" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH37" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ37" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK37" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AL37" t="s" s="2">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL37">
+  <autoFilter ref="A1:AL34">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5346,7 +4991,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI36">
+  <conditionalFormatting sqref="A2:AI33">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -868,7 +868,7 @@
 </t>
   </si>
   <si>
-    <t>Upper limit on medication per unit of time</t>
+    <t>Maximale Menge pro Zeiteinheit</t>
   </si>
   <si>
     <t>Upper limit on medication per unit of time.</t>
@@ -893,7 +893,7 @@
 </t>
   </si>
   <si>
-    <t>Upper limit on medication per administration</t>
+    <t>Maximal Menge pro Abgabe</t>
   </si>
   <si>
     <t>Upper limit on medication per administration.</t>
@@ -911,7 +911,7 @@
     <t>Dosage.maxDosePerLifetime</t>
   </si>
   <si>
-    <t>Upper limit on medication per lifetime of the patient</t>
+    <t>Maximale Lebenszeitdosis</t>
   </si>
   <si>
     <t>Upper limit on medication per lifetime of the patient.</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:01:54+00:00</t>
+    <t>2026-04-22T10:11:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-28T11:58:02+00:00</t>
+    <t>2026-04-29T14:27:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T14:27:58+00:00</t>
+    <t>2026-04-30T15:16:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:23:35+00:00</t>
+    <t>2026-05-04T14:46:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-emed-dosage.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
